--- a/PROPEM.xlsx
+++ b/PROPEM.xlsx
@@ -52,7 +52,7 @@
     <t>20042991</t>
   </si>
   <si>
-    <t>IDM GULA PSR PRM 1KG</t>
+    <t>IDM GULA P.P PT 1KG</t>
   </si>
   <si>
     <t>PT,(E-2B)</t>
@@ -61,7 +61,7 @@
     <t>20052296</t>
   </si>
   <si>
-    <t>IDM GULA PRM KNG 1KG</t>
+    <t>IDM GULA PRM KN 1 KG</t>
   </si>
   <si>
     <t>20077116</t>
